--- a/diseases/d113/2010-2014.xlsx
+++ b/diseases/d113/2010-2014.xlsx
@@ -1061,9 +1061,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1457,9 +1454,6 @@
       <c r="O6" t="n">
         <v>5</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.01025234454459675</v>
       </c>
@@ -2049,9 +2043,6 @@
       <c r="O10" t="n">
         <v>3</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.006151406726758049</v>
       </c>
@@ -2641,9 +2632,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -3233,9 +3221,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
@@ -3825,9 +3810,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -4417,9 +4399,6 @@
       <c r="O26" t="n">
         <v>1</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.00205046890891935</v>
       </c>
@@ -5009,9 +4988,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -5601,9 +5577,6 @@
       <c r="O34" t="n">
         <v>1</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0.00205046890891935</v>
       </c>
@@ -6193,9 +6166,6 @@
       <c r="O38" t="n">
         <v>2</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.0041009378178387</v>
       </c>
@@ -6785,9 +6755,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
@@ -7377,9 +7344,6 @@
       <c r="O46" t="n">
         <v>1</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.00205046890891935</v>
       </c>
@@ -7969,9 +7933,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -8561,9 +8522,6 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
@@ -8957,9 +8915,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -9401,9 +9356,6 @@
       <c r="O59" t="n">
         <v>0</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
@@ -9993,9 +9945,6 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -10585,9 +10534,6 @@
       <c r="O67" t="n">
         <v>1</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0.002035513875197372</v>
       </c>
@@ -11177,9 +11123,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -11769,9 +11712,6 @@
       <c r="O75" t="n">
         <v>2</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0.004071027750394744</v>
       </c>
@@ -12361,9 +12301,6 @@
       <c r="O79" t="n">
         <v>3</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.006106541625592117</v>
       </c>
@@ -12953,9 +12890,6 @@
       <c r="O83" t="n">
         <v>1</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0.002035513875197372</v>
       </c>
@@ -13545,9 +13479,6 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
@@ -14137,9 +14068,6 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
@@ -14729,9 +14657,6 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0</v>
       </c>
@@ -15321,9 +15246,6 @@
       <c r="O99" t="n">
         <v>1</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.002035513875197372</v>
       </c>
@@ -15765,9 +15687,6 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
@@ -16161,9 +16080,6 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
@@ -16753,9 +16669,6 @@
       <c r="O108" t="n">
         <v>1</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.002016146124787207</v>
       </c>
@@ -17345,9 +17258,6 @@
       <c r="O112" t="n">
         <v>1</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.002016146124787207</v>
       </c>
@@ -17937,9 +17847,6 @@
       <c r="O116" t="n">
         <v>1</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.002016146124787207</v>
       </c>
@@ -18529,9 +18436,6 @@
       <c r="O120" t="n">
         <v>2</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.004032292249574414</v>
       </c>
@@ -19121,9 +19025,6 @@
       <c r="O124" t="n">
         <v>2</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.004032292249574414</v>
       </c>
@@ -19713,9 +19614,6 @@
       <c r="O128" t="n">
         <v>2</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0.004032292249574414</v>
       </c>
@@ -20305,9 +20203,6 @@
       <c r="O132" t="n">
         <v>0</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0</v>
       </c>
@@ -20897,9 +20792,6 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0</v>
       </c>
@@ -21933,9 +21825,6 @@
       <c r="O143" t="n">
         <v>0</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0</v>
       </c>
@@ -23117,9 +23006,6 @@
       <c r="O151" t="n">
         <v>1</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0.002016146124787207</v>
       </c>
@@ -24449,9 +24335,6 @@
       <c r="O160" t="n">
         <v>0</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0</v>
       </c>
@@ -25781,9 +25664,6 @@
       <c r="O169" t="n">
         <v>0</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>0</v>
       </c>
@@ -26177,9 +26057,6 @@
       <c r="O171" t="n">
         <v>0</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0</v>
       </c>
@@ -26325,9 +26202,6 @@
       <c r="O172" t="n">
         <v>0</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0</v>
       </c>
@@ -27905,9 +27779,6 @@
       <c r="O182" t="n">
         <v>0</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>0</v>
       </c>
@@ -28053,9 +27924,6 @@
       <c r="O183" t="n">
         <v>0</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>0</v>
       </c>
@@ -29485,9 +29353,6 @@
       <c r="O192" t="n">
         <v>1</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0.001997157465750572</v>
       </c>
@@ -29633,9 +29498,6 @@
       <c r="O193" t="n">
         <v>1</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0.01968455694343711</v>
       </c>
@@ -31065,9 +30927,6 @@
       <c r="O202" t="n">
         <v>0</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="R202" t="n">
         <v>0</v>
       </c>
@@ -31213,9 +31072,6 @@
       <c r="O203" t="n">
         <v>1</v>
       </c>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
       <c r="R203" t="n">
         <v>0.01968455694343711</v>
       </c>
@@ -32645,9 +32501,6 @@
       <c r="O212" t="n">
         <v>0</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>0</v>
       </c>
@@ -32793,9 +32646,6 @@
       <c r="O213" t="n">
         <v>1</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>0.01968455694343711</v>
       </c>
@@ -34373,9 +34223,6 @@
       <c r="O223" t="n">
         <v>2</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="R223" t="n">
         <v>0.003994314931501143</v>
       </c>
@@ -34521,9 +34368,6 @@
       <c r="O224" t="n">
         <v>0</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>0</v>
       </c>
@@ -35953,9 +35797,6 @@
       <c r="O233" t="n">
         <v>2</v>
       </c>
-      <c r="Q233" t="n">
-        <v>0</v>
-      </c>
       <c r="R233" t="n">
         <v>0.003994314931501143</v>
       </c>
@@ -36101,9 +35942,6 @@
       <c r="O234" t="n">
         <v>0</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="R234" t="n">
         <v>0</v>
       </c>
@@ -37533,9 +37371,6 @@
       <c r="O243" t="n">
         <v>2</v>
       </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
       <c r="R243" t="n">
         <v>0.003994314931501143</v>
       </c>
@@ -37681,9 +37516,6 @@
       <c r="O244" t="n">
         <v>0</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="R244" t="n">
         <v>0</v>
       </c>
@@ -39261,9 +39093,6 @@
       <c r="O254" t="n">
         <v>1</v>
       </c>
-      <c r="Q254" t="n">
-        <v>0</v>
-      </c>
       <c r="R254" t="n">
         <v>0.001997157465750572</v>
       </c>
@@ -39409,9 +39238,6 @@
       <c r="O255" t="n">
         <v>1</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="R255" t="n">
         <v>0.01968455694343711</v>
       </c>
@@ -40841,9 +40667,6 @@
       <c r="O264" t="n">
         <v>1</v>
       </c>
-      <c r="Q264" t="n">
-        <v>0</v>
-      </c>
       <c r="R264" t="n">
         <v>0.001997157465750572</v>
       </c>
@@ -40989,9 +40812,6 @@
       <c r="O265" t="n">
         <v>0</v>
       </c>
-      <c r="Q265" t="n">
-        <v>0</v>
-      </c>
       <c r="R265" t="n">
         <v>0</v>
       </c>
@@ -42569,9 +42389,6 @@
       <c r="O275" t="n">
         <v>1</v>
       </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
       <c r="R275" t="n">
         <v>0.001997157465750572</v>
       </c>
@@ -42717,9 +42534,6 @@
       <c r="O276" t="n">
         <v>0</v>
       </c>
-      <c r="Q276" t="n">
-        <v>0</v>
-      </c>
       <c r="R276" t="n">
         <v>0</v>
       </c>
@@ -44149,9 +43963,6 @@
       <c r="O285" t="n">
         <v>1</v>
       </c>
-      <c r="Q285" t="n">
-        <v>0</v>
-      </c>
       <c r="R285" t="n">
         <v>0.001997157465750572</v>
       </c>
@@ -44297,9 +44108,6 @@
       <c r="O286" t="n">
         <v>0</v>
       </c>
-      <c r="Q286" t="n">
-        <v>0</v>
-      </c>
       <c r="R286" t="n">
         <v>0</v>
       </c>
@@ -45877,9 +45685,6 @@
       <c r="O296" t="n">
         <v>0</v>
       </c>
-      <c r="Q296" t="n">
-        <v>0</v>
-      </c>
       <c r="R296" t="n">
         <v>0</v>
       </c>
@@ -46273,9 +46078,6 @@
       <c r="O298" t="n">
         <v>3</v>
       </c>
-      <c r="Q298" t="n">
-        <v>0</v>
-      </c>
       <c r="R298" t="n">
         <v>0.005936003295510736</v>
       </c>
@@ -46421,9 +46223,6 @@
       <c r="O299" t="n">
         <v>0</v>
       </c>
-      <c r="Q299" t="n">
-        <v>0</v>
-      </c>
       <c r="R299" t="n">
         <v>0</v>
       </c>
@@ -48001,9 +47800,6 @@
       <c r="O309" t="n">
         <v>1</v>
       </c>
-      <c r="Q309" t="n">
-        <v>0</v>
-      </c>
       <c r="R309" t="n">
         <v>0.001978667765170246</v>
       </c>
@@ -48149,9 +47945,6 @@
       <c r="O310" t="n">
         <v>0</v>
       </c>
-      <c r="Q310" t="n">
-        <v>0</v>
-      </c>
       <c r="R310" t="n">
         <v>0</v>
       </c>
@@ -49581,9 +49374,6 @@
       <c r="O319" t="n">
         <v>0</v>
       </c>
-      <c r="Q319" t="n">
-        <v>0</v>
-      </c>
       <c r="R319" t="n">
         <v>0</v>
       </c>
@@ -49729,9 +49519,6 @@
       <c r="O320" t="n">
         <v>0</v>
       </c>
-      <c r="Q320" t="n">
-        <v>0</v>
-      </c>
       <c r="R320" t="n">
         <v>0</v>
       </c>
@@ -51013,9 +50800,6 @@
       <c r="O328" t="n">
         <v>0</v>
       </c>
-      <c r="Q328" t="n">
-        <v>0</v>
-      </c>
       <c r="R328" t="n">
         <v>0</v>
       </c>
@@ -51161,9 +50945,6 @@
       <c r="O329" t="n">
         <v>0</v>
       </c>
-      <c r="Q329" t="n">
-        <v>0</v>
-      </c>
       <c r="R329" t="n">
         <v>0</v>
       </c>
@@ -52593,9 +52374,6 @@
       <c r="O338" t="n">
         <v>1</v>
       </c>
-      <c r="Q338" t="n">
-        <v>0</v>
-      </c>
       <c r="R338" t="n">
         <v>0.001978667765170246</v>
       </c>
@@ -52741,9 +52519,6 @@
       <c r="O339" t="n">
         <v>0</v>
       </c>
-      <c r="Q339" t="n">
-        <v>0</v>
-      </c>
       <c r="R339" t="n">
         <v>0</v>
       </c>
@@ -54321,9 +54096,6 @@
       <c r="O349" t="n">
         <v>1</v>
       </c>
-      <c r="Q349" t="n">
-        <v>0</v>
-      </c>
       <c r="R349" t="n">
         <v>0.001978667765170246</v>
       </c>
@@ -54469,9 +54241,6 @@
       <c r="O350" t="n">
         <v>0</v>
       </c>
-      <c r="Q350" t="n">
-        <v>0</v>
-      </c>
       <c r="R350" t="n">
         <v>0</v>
       </c>
@@ -55901,9 +55670,6 @@
       <c r="O359" t="n">
         <v>0</v>
       </c>
-      <c r="Q359" t="n">
-        <v>0</v>
-      </c>
       <c r="R359" t="n">
         <v>0</v>
       </c>
@@ -56049,9 +55815,6 @@
       <c r="O360" t="n">
         <v>0</v>
       </c>
-      <c r="Q360" t="n">
-        <v>0</v>
-      </c>
       <c r="R360" t="n">
         <v>0</v>
       </c>
@@ -57629,9 +57392,6 @@
       <c r="O370" t="n">
         <v>0</v>
       </c>
-      <c r="Q370" t="n">
-        <v>0</v>
-      </c>
       <c r="R370" t="n">
         <v>0</v>
       </c>
@@ -57777,9 +57537,6 @@
       <c r="O371" t="n">
         <v>0</v>
       </c>
-      <c r="Q371" t="n">
-        <v>0</v>
-      </c>
       <c r="R371" t="n">
         <v>0</v>
       </c>
@@ -59209,9 +58966,6 @@
       <c r="O380" t="n">
         <v>0</v>
       </c>
-      <c r="Q380" t="n">
-        <v>0</v>
-      </c>
       <c r="R380" t="n">
         <v>0</v>
       </c>
@@ -59357,9 +59111,6 @@
       <c r="O381" t="n">
         <v>1</v>
       </c>
-      <c r="Q381" t="n">
-        <v>0</v>
-      </c>
       <c r="R381" t="n">
         <v>0.01946511802187685</v>
       </c>
@@ -60789,9 +60540,6 @@
       <c r="O390" t="n">
         <v>0</v>
       </c>
-      <c r="Q390" t="n">
-        <v>0</v>
-      </c>
       <c r="R390" t="n">
         <v>0</v>
       </c>
@@ -60937,9 +60685,6 @@
       <c r="O391" t="n">
         <v>0</v>
       </c>
-      <c r="Q391" t="n">
-        <v>0</v>
-      </c>
       <c r="R391" t="n">
         <v>0</v>
       </c>
@@ -62517,9 +62262,6 @@
       <c r="O401" t="n">
         <v>0</v>
       </c>
-      <c r="Q401" t="n">
-        <v>0</v>
-      </c>
       <c r="R401" t="n">
         <v>0</v>
       </c>
@@ -62665,9 +62407,6 @@
       <c r="O402" t="n">
         <v>0</v>
       </c>
-      <c r="Q402" t="n">
-        <v>0</v>
-      </c>
       <c r="R402" t="n">
         <v>0</v>
       </c>
@@ -64097,9 +63836,6 @@
       <c r="O411" t="n">
         <v>2</v>
       </c>
-      <c r="Q411" t="n">
-        <v>0</v>
-      </c>
       <c r="R411" t="n">
         <v>0.003957335530340491</v>
       </c>
@@ -64243,9 +63979,6 @@
         <v>0</v>
       </c>
       <c r="O412" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q412" t="n">
         <v>0</v>
       </c>
       <c r="R412" t="n">
